--- a/partner_results/pato/ClassMissingLastUpdateOn_pato.xlsx
+++ b/partner_results/pato/ClassMissingLastUpdateOn_pato.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>length [pato]</t>
+          <t>physical object quality [pato]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>morphology</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A 1-dimensional extent quality which is equal to the distance between two points.</t>
+          <t>A quality which inheres in a continuant.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>physical object quality [pato]</t>
+          <t>quality of a solid [pato]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>quality of a substance [pato]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A quality which inheres in a continuant.</t>
+          <t>A physical quality inhering in a bearer by virtue of the bearer's exhibiting the physical characteristics of an entity characterized by particles arranged such that their shape and volume are relatively stable.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>optical quality [pato]</t>
+          <t>length [pato]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>electromagnetic (EM) radiation quality</t>
+          <t>morphology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>An EM radiation quality in which the EM radiation is within the fiat range of the spectrum visible deemed to be light.</t>
+          <t>A 1-dimensional extent quality which is equal to the distance between two points.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -541,18 +541,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quality of a solid [pato]</t>
+          <t>optical quality [pato]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quality of a substance [pato]</t>
+          <t>electromagnetic (EM) radiation quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A physical quality inhering in a bearer by virtue of the bearer's exhibiting the physical characteristics of an entity characterized by particles arranged such that their shape and volume are relatively stable.</t>
+          <t>An EM radiation quality in which the EM radiation is within the fiat range of the spectrum visible deemed to be light.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
